--- a/datos/excel/6a06af219064f0305ee69cd2/Registros - Naiki.xlsx
+++ b/datos/excel/6a06af219064f0305ee69cd2/Registros - Naiki.xlsx
@@ -8,6 +8,8 @@
     <sheet sheetId="2" name="7. Limpieza campanatrampa" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="1. Recepción MP" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="5. Limpieza salón (Sal)" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="2. Calidad del agua" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="4. Verificación plagas (Sal)" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -81,8 +83,49 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A6" authorId="0">
+      <text>
+        <r>
+          <t>Día feriado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0">
+      <text>
+        <r>
+          <t>Día feriado</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A6" authorId="0">
+      <text>
+        <r>
+          <t>Día feriado</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="94">
   <si>
     <t>FORMATO DE EJECUCIÓN Y CONTROL DE LIMPIEZA Y DESINFECCIÓN — BAÑO</t>
   </si>
@@ -226,13 +269,151 @@
   </si>
   <si>
     <t>Ambiente [DO] · Alimentos y empaques [DO] · Techo, lámparas [HS] · Piso [HS] · Canastillas [HS] · Tostadora [HS]</t>
+  </si>
+  <si>
+    <t>FORMATO DE CONTROL DE CALIDAD DEL AGUA POTABLE</t>
+  </si>
+  <si>
+    <t>PLAN DE SANEAMIENTO BÁSICO  ·  PROGRAMA DE ABASTECIMIENTO DE AGUA POTABLE  ·  Código AA-F-01  ·  Versión 03</t>
+  </si>
+  <si>
+    <t>Carpeta</t>
+  </si>
+  <si>
+    <t>Hora muestreo</t>
+  </si>
+  <si>
+    <t>Punto de muestreo</t>
+  </si>
+  <si>
+    <t>pH (valor)</t>
+  </si>
+  <si>
+    <t>pH (C/NC)</t>
+  </si>
+  <si>
+    <t>Cloro (mg/L)</t>
+  </si>
+  <si>
+    <t>Cloro (C/NC)</t>
+  </si>
+  <si>
+    <t>Sabor</t>
+  </si>
+  <si>
+    <t>Cocina</t>
+  </si>
+  <si>
+    <t>06:06</t>
+  </si>
+  <si>
+    <t>Llave #2</t>
+  </si>
+  <si>
+    <t>samuel</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>Llave #7</t>
+  </si>
+  <si>
+    <t>andres</t>
+  </si>
+  <si>
+    <t>sábado, 02 de mayo de 2026</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>Llave #3</t>
+  </si>
+  <si>
+    <t>domingo, 03 de mayo de 2026</t>
+  </si>
+  <si>
+    <t>04:44</t>
+  </si>
+  <si>
+    <t>lunes, 04 de mayo de 2026</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>Llave #5</t>
+  </si>
+  <si>
+    <t>sam</t>
+  </si>
+  <si>
+    <t>martes, 05 de mayo de 2026</t>
+  </si>
+  <si>
+    <t>11:34</t>
+  </si>
+  <si>
+    <t>miércoles, 06 de mayo de 2026</t>
+  </si>
+  <si>
+    <t>02:02</t>
+  </si>
+  <si>
+    <t>Llave #6</t>
+  </si>
+  <si>
+    <t>jueves, 07 de mayo de 2026</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>nico</t>
+  </si>
+  <si>
+    <t>viernes, 08 de mayo de 2026</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>FORMATO DE VERIFICACIÓN DIARIA DE PLAGAS</t>
+  </si>
+  <si>
+    <t>PLAN DE SANEAMIENTO BÁSICO  ·  PROGRAMA DE CONTROL INTEGRADO DE PLAGAS  ·  Código CP-F-01</t>
+  </si>
+  <si>
+    <t>Áreas inspeccionadas</t>
+  </si>
+  <si>
+    <t>Tipo de control</t>
+  </si>
+  <si>
+    <t>Novedad</t>
+  </si>
+  <si>
+    <t>Cocina, Bodega, Salón, Externas</t>
+  </si>
+  <si>
+    <t>Preventivo</t>
+  </si>
+  <si>
+    <t>Café</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -263,8 +444,12 @@
       <b/>
       <color rgb="FF065F46"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF991B1B"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,6 +469,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -310,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -332,6 +522,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1171,6 +1373,664 @@
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF16C2A3"/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="12" width="8" customWidth="1"/>
+    <col min="13" max="13" width="36" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="5">
+        <v>6.79</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="5">
+        <v>6.89</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="5">
+        <v>6.8</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="5">
+        <v>6.89</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="5">
+        <v>6.69</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6.8</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="5">
+        <v>6.8</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A4:N4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF16C2A3"/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
